--- a/dataEDT-ELT-S2-2026.xlsx
+++ b/dataEDT-ELT-S2-2026.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="947">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2258,7 +2258,7 @@
     <t>Cours-Mathématiques 1</t>
   </si>
   <si>
-    <t>Cours-MAT1-L1MCIL</t>
+    <t>Cours-MAT1-MCIL1</t>
   </si>
   <si>
     <t>Bahlil</t>
@@ -2267,13 +2267,13 @@
     <t>A10/Section B</t>
   </si>
   <si>
-    <t>L1MCIL</t>
+    <t>MCIL1</t>
   </si>
   <si>
     <t>Cours-Structure de la matière</t>
   </si>
   <si>
-    <t>Cours-SM-L1MCIL</t>
+    <t>Cours-SM-MCIL1</t>
   </si>
   <si>
     <t>Badis</t>
@@ -2282,397 +2282,595 @@
     <t>TD-Informatique 1</t>
   </si>
   <si>
-    <t>TD-INFO1-L1MCIL-G2</t>
+    <t>TD-INFO1-MCIL1-G2</t>
   </si>
   <si>
     <t>Non identifié</t>
   </si>
   <si>
+    <t>Salle micro/G2</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G7</t>
+  </si>
+  <si>
+    <t>Salle micro/G7</t>
+  </si>
+  <si>
+    <t>TD-Mathématiques 1</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G1</t>
+  </si>
+  <si>
+    <t>A08/G1</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G6</t>
+  </si>
+  <si>
+    <t>A08/G6</t>
+  </si>
+  <si>
+    <t>TD-Physique 1</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G3</t>
+  </si>
+  <si>
+    <t>SACI</t>
+  </si>
+  <si>
+    <t>A09/G3</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G8</t>
+  </si>
+  <si>
+    <t>Zidi</t>
+  </si>
+  <si>
+    <t>A09/G8</t>
+  </si>
+  <si>
+    <t>TD-Structure de la matière</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G5</t>
+  </si>
+  <si>
+    <t>HEMMAR</t>
+  </si>
+  <si>
+    <t>A09/G5</t>
+  </si>
+  <si>
+    <t>TP-Informatique 1</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG05</t>
+  </si>
+  <si>
+    <t>13h-14h30</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG05</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG06</t>
+  </si>
+  <si>
+    <t>BENCELLA</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG06</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG15</t>
+  </si>
+  <si>
+    <t>BENHALOUCHE</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG15</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG16</t>
+  </si>
+  <si>
+    <t>ZIAN</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG16</t>
+  </si>
+  <si>
+    <t>TP-Chimie 1</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG01</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG01</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG02</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG02</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG11</t>
+  </si>
+  <si>
+    <t>MOKADEM</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG11</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG12</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG12</t>
+  </si>
+  <si>
+    <t>TP-Physique 1</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG07</t>
+  </si>
+  <si>
+    <t>BENSSADIK</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG07</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG08</t>
+  </si>
+  <si>
+    <t>BOULARAF</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG08</t>
+  </si>
+  <si>
+    <t>Cours-Informatique 1</t>
+  </si>
+  <si>
+    <t>Cours-INFO1-MCIL1</t>
+  </si>
+  <si>
+    <t>Beddad</t>
+  </si>
+  <si>
+    <t>A10/Section A</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G3</t>
+  </si>
+  <si>
+    <t>Salle micro/G3</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G8</t>
+  </si>
+  <si>
+    <t>Salle micro/G8</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G2</t>
+  </si>
+  <si>
+    <t>ABDELI</t>
+  </si>
+  <si>
+    <t>A08/G2</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G7</t>
+  </si>
+  <si>
+    <t>A08/G7</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G4</t>
+  </si>
+  <si>
+    <t>A09/G4</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G1</t>
+  </si>
+  <si>
+    <t>A09/G1</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G6</t>
+  </si>
+  <si>
+    <t>MECHTEM</t>
+  </si>
+  <si>
+    <t>A09/G6</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG07</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG07</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG08</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG08</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG03</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG03</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG04</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG04</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG13</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG13</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG14</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG14</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG09</t>
+  </si>
+  <si>
+    <t>DRIEF</t>
+  </si>
+  <si>
+    <t>Labo Physique /SG09</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG10</t>
+  </si>
+  <si>
+    <t>Mekhalef</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG10</t>
+  </si>
+  <si>
+    <t>Cours-Physique 1</t>
+  </si>
+  <si>
+    <t>Cours-PHY1-MCIL1</t>
+  </si>
+  <si>
+    <t>Bendaoud</t>
+  </si>
+  <si>
+    <t>A9/Section B</t>
+  </si>
+  <si>
+    <t>Cours-Méthodologie de la rédaction</t>
+  </si>
+  <si>
+    <t>Cours-MR-MCIL1</t>
+  </si>
+  <si>
+    <t>9h30-10h30</t>
+  </si>
+  <si>
+    <t>Cours-Langue étrangère 1</t>
+  </si>
+  <si>
+    <t>Cours-LE1-MCIL1</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G1</t>
+  </si>
+  <si>
+    <t>Salle micro/G1</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G6</t>
+  </si>
+  <si>
+    <t>Salle micro/G6</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G5</t>
+  </si>
+  <si>
+    <t>A08/G5</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G2</t>
+  </si>
+  <si>
+    <t>A09/G2</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G7</t>
+  </si>
+  <si>
+    <t>A09/G7</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G4</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG05</t>
+  </si>
+  <si>
+    <t>Labo Physique /SG05</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG06</t>
+  </si>
+  <si>
+    <t>TURKI</t>
+  </si>
+  <si>
+    <t>Labo Physique /SG06</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG15</t>
+  </si>
+  <si>
+    <t>Labo Physique /SG15</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG16</t>
+  </si>
+  <si>
+    <t>Labo Physique /SG16</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG03</t>
+  </si>
+  <si>
+    <t>14h30-16h</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG03</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG04</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG04</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG13</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG13</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG14</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG14</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG09</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG09</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG10</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG10</t>
+  </si>
+  <si>
+    <t>Cours-Les métiers en Sciences et Technologies 1</t>
+  </si>
+  <si>
+    <t>Cours-LMST-MCIL1</t>
+  </si>
+  <si>
+    <t>A11/Section B</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G4</t>
+  </si>
+  <si>
+    <t>Salle micro/G4</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G3</t>
+  </si>
+  <si>
+    <t>A08/G3</t>
+  </si>
+  <si>
+    <t>TD-MAT1-MCIL1-G8</t>
+  </si>
+  <si>
+    <t>A08/G8</t>
+  </si>
+  <si>
+    <t>TD-PHY1-MCIL1-G5</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G2</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G7</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG09</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG09</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG10</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG10</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG05</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG05</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG06</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG06</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG15</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG15</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG16</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG16</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG01</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG01</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG02</t>
+  </si>
+  <si>
+    <t>Labo Physique 2/SG02</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG11</t>
+  </si>
+  <si>
+    <t>Labo Physique 3/SG11</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG12</t>
+  </si>
+  <si>
+    <t>Labo Physique 4/SG12</t>
+  </si>
+  <si>
+    <t>Cours-Dimension éthique et déontologie</t>
+  </si>
+  <si>
+    <t>Cours-DE-MCIL1</t>
+  </si>
+  <si>
+    <t>Ouari</t>
+  </si>
+  <si>
+    <t>A10/Section A-B</t>
+  </si>
+  <si>
+    <t>TD-INFO1-MCIL1-G5</t>
+  </si>
+  <si>
     <t>Salle micro</t>
   </si>
   <si>
-    <t>TD-INFO1-L1MCIL-G7</t>
-  </si>
-  <si>
-    <t>TD-Mathématiques 1</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G1</t>
+    <t>TD-MAT1-MCIL1-G4</t>
   </si>
   <si>
     <t>A08/G1-G8</t>
   </si>
   <si>
-    <t>TD-MAT1-L1MCIL-G6</t>
-  </si>
-  <si>
-    <t>TD-Physique 1</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G3</t>
-  </si>
-  <si>
-    <t>SACI</t>
+    <t>TD-PHY1-MCIL1-G1</t>
   </si>
   <si>
     <t>A09/G1-G8</t>
   </si>
   <si>
-    <t>TD-PHY1-L1MCIL-G8</t>
-  </si>
-  <si>
-    <t>Zidi</t>
-  </si>
-  <si>
-    <t>TD-Structure de la matière</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G5</t>
-  </si>
-  <si>
-    <t>HEMMAR</t>
-  </si>
-  <si>
-    <t>A09/G5</t>
-  </si>
-  <si>
-    <t>TP-Informatique 1</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG05</t>
-  </si>
-  <si>
-    <t>13h-14h30</t>
-  </si>
-  <si>
-    <t>Salle micro2/SG11-12,SG31-32,SG61-62,SG81-82</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG06</t>
-  </si>
-  <si>
-    <t>BENCELLA</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG15</t>
-  </si>
-  <si>
-    <t>BENHALOUCHE</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG16</t>
-  </si>
-  <si>
-    <t>ZIAN</t>
-  </si>
-  <si>
-    <t>TP-TP Chimie 1</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG01</t>
-  </si>
-  <si>
-    <t>Labo Chimie/SG12,SG22,SG32,SG42,SG52,SG62,SG72,SG82</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG02</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG11</t>
-  </si>
-  <si>
-    <t>MOKADEM</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG12</t>
-  </si>
-  <si>
-    <t>ND</t>
-  </si>
-  <si>
-    <t>TP-TP Physique 1</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG07</t>
-  </si>
-  <si>
-    <t>BENSSADIK</t>
-  </si>
-  <si>
-    <t>Labo Physique 1/SG11,SG21,SG31,SG41,SG51,SG61,SG71,SG81</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG08</t>
-  </si>
-  <si>
-    <t>BOULARAF</t>
-  </si>
-  <si>
-    <t>Cours-Informatique 1</t>
-  </si>
-  <si>
-    <t>Cours-INFO1-L1MCIL</t>
-  </si>
-  <si>
-    <t>Beddad</t>
-  </si>
-  <si>
-    <t>A10/Section A</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G3</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G8</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G2</t>
-  </si>
-  <si>
-    <t>ABDELI</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G7</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G4</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G1</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G6</t>
-  </si>
-  <si>
-    <t>MECHTEM</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG07</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG08</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG03</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG04</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG13</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG14</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG09</t>
-  </si>
-  <si>
-    <t>DRIEF</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG10</t>
-  </si>
-  <si>
-    <t>Mekhalef</t>
-  </si>
-  <si>
-    <t>Cours-Physique 1</t>
-  </si>
-  <si>
-    <t>Cours-PHY1-L1MCIL</t>
-  </si>
-  <si>
-    <t>Bendaoud</t>
-  </si>
-  <si>
-    <t>A9/Section B</t>
-  </si>
-  <si>
-    <t>Cours-Méthodologie de la rédaction</t>
-  </si>
-  <si>
-    <t>Cours-MR-L1MCIL</t>
-  </si>
-  <si>
-    <t>9h30-10h30</t>
-  </si>
-  <si>
-    <t>Cours-Langue étrangère 1</t>
-  </si>
-  <si>
-    <t>Cours-LE1-L1MCIL</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G1</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G6</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G5</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G2</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G7</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G4</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG05</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG06</t>
-  </si>
-  <si>
-    <t>TURKI</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG15</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG16</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG03</t>
-  </si>
-  <si>
-    <t>14h30-16h</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG04</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG13</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG14</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG09</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG10</t>
-  </si>
-  <si>
-    <t>Cours-Les métiers en Sciences et Technologies 1</t>
-  </si>
-  <si>
-    <t>Cours-LMST-L1MCIL</t>
-  </si>
-  <si>
-    <t>A11/Section B</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G4</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G3</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G8</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G5</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G2</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G7</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG09</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG10</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG05</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG06</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG15</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG16</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG01</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG02</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG11</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG12</t>
-  </si>
-  <si>
-    <t>Cours-Dimension éthique et déontologie</t>
-  </si>
-  <si>
-    <t>Cours-DE-L1MCIL</t>
-  </si>
-  <si>
-    <t>Ouari</t>
-  </si>
-  <si>
-    <t>A10/Section A-B</t>
-  </si>
-  <si>
-    <t>TD-INFO1-L1MCIL-G5</t>
-  </si>
-  <si>
-    <t>TD-MAT1-L1MCIL-G4</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G1</t>
-  </si>
-  <si>
-    <t>TD-PHY1-L1MCIL-G6</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G3</t>
-  </si>
-  <si>
-    <t>TD-SM-L1MCIL-G8</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG01</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG02</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG11</t>
-  </si>
-  <si>
-    <t>TP-INFO1-L1MCIL-SG12</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG07</t>
-  </si>
-  <si>
-    <t>TP-TPCH1-L1MCIL-SG08</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG03</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG04</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG13</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-L1MCIL-SG14</t>
+    <t>TD-PHY1-MCIL1-G6</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G3</t>
+  </si>
+  <si>
+    <t>TD-SM-MCIL1-G8</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG01</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG01</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG02</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG02</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG11</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG11</t>
+  </si>
+  <si>
+    <t>TP-INFO1-MCIL1-SG12</t>
+  </si>
+  <si>
+    <t>Salle micro2/SG12</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG07</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG07</t>
+  </si>
+  <si>
+    <t>TP-TPCH1-MCIL1-SG08</t>
+  </si>
+  <si>
+    <t>Labo Chimie/SG08</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG03</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG03</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG04</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG04</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG13</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG13</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-MCIL1-SG14</t>
+  </si>
+  <si>
+    <t>Labo Physique 1/SG14</t>
   </si>
 </sst>
 </file>
@@ -3326,29 +3524,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -14606,7 +14795,7 @@
       <c r="F474" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="G474" s="4" t="s">
+      <c r="G474" s="3" t="s">
         <v>745</v>
       </c>
     </row>
@@ -14629,398 +14818,398 @@
       <c r="F475" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="G475" s="4" t="s">
+      <c r="G475" s="3" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="476" ht="25.5" spans="1:7">
-      <c r="A476" s="5" t="s">
+    <row r="476" spans="1:7">
+      <c r="A476" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B476" s="5" t="s">
+      <c r="B476" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C476" s="5" t="s">
+      <c r="C476" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D476" s="5" t="s">
+      <c r="D476" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E476" s="5" t="s">
+      <c r="E476" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F476" s="5" t="s">
+      <c r="F476" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="G476" s="6" t="s">
+      <c r="G476" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="477" ht="25.5" spans="1:7">
-      <c r="A477" s="5" t="s">
+    <row r="477" spans="1:7">
+      <c r="A477" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B477" s="5" t="s">
+      <c r="B477" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C477" s="5" t="s">
+      <c r="C477" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D477" s="5" t="s">
+      <c r="D477" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E477" s="5" t="s">
+      <c r="E477" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F477" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G477" s="6" t="s">
+      <c r="F477" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="G477" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="478" spans="1:7">
-      <c r="A478" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B478" s="5" t="s">
+      <c r="A478" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="C478" s="5" t="s">
+      <c r="B478" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C478" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="D478" s="5" t="s">
+      <c r="D478" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E478" s="5" t="s">
+      <c r="E478" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F478" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G478" s="6" t="s">
+      <c r="F478" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="G478" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="479" spans="1:7">
-      <c r="A479" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B479" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="C479" s="5" t="s">
+      <c r="A479" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C479" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="D479" s="5" t="s">
+      <c r="D479" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E479" s="5" t="s">
+      <c r="E479" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F479" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G479" s="6" t="s">
+      <c r="F479" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="G479" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="480" spans="1:7">
-      <c r="A480" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B480" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="C480" s="5" t="s">
+      <c r="A480" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="D480" s="5" t="s">
+      <c r="B480" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D480" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E480" s="5" t="s">
+      <c r="E480" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F480" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G480" s="6" t="s">
+      <c r="F480" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="G480" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="481" spans="1:7">
-      <c r="A481" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B481" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="C481" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="D481" s="5" t="s">
+      <c r="A481" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="D481" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E481" s="5" t="s">
+      <c r="E481" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F481" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G481" s="6" t="s">
+      <c r="F481" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="G481" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="482" spans="1:7">
-      <c r="A482" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B482" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="C482" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="D482" s="5" t="s">
+      <c r="A482" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D482" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E482" s="5" t="s">
+      <c r="E482" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F482" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G482" s="6" t="s">
+      <c r="F482" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G482" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="483" ht="38.25" spans="1:7">
-      <c r="A483" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B483" s="7" t="s">
+    <row r="483" ht="25.5" spans="1:7">
+      <c r="A483" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="C483" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D483" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E483" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F483" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="G483" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="484" ht="25.5" spans="1:7">
+      <c r="A484" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C484" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="D484" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E484" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F484" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="G484" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="485" ht="25.5" spans="1:7">
+      <c r="A485" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B485" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="C485" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D485" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E485" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F485" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="G485" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="486" ht="25.5" spans="1:7">
+      <c r="A486" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B486" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="D486" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E486" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F486" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="G486" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="487" ht="25.5" spans="1:7">
+      <c r="A487" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B487" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C487" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D487" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E487" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F487" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="G487" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="488" ht="25.5" spans="1:7">
+      <c r="A488" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="C488" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="C483" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D483" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E483" s="7" t="s">
+      <c r="D488" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E488" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F483" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G483" s="8" t="s">
+      <c r="F488" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="G488" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="484" ht="38.25" spans="1:7">
-      <c r="A484" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B484" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="C484" s="7" t="s">
+    <row r="489" ht="25.5" spans="1:7">
+      <c r="A489" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B489" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="C489" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D489" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D484" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E484" s="7" t="s">
+      <c r="E489" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F484" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G484" s="8" t="s">
+      <c r="F489" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="G489" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="485" ht="38.25" spans="1:7">
-      <c r="A485" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B485" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="C485" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D485" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E485" s="7" t="s">
+    <row r="490" ht="25.5" spans="1:7">
+      <c r="A490" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B490" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C490" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D490" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E490" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F485" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G485" s="8" t="s">
+      <c r="F490" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G490" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="486" ht="38.25" spans="1:7">
-      <c r="A486" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B486" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="C486" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D486" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E486" s="7" t="s">
+    <row r="491" ht="25.5" spans="1:7">
+      <c r="A491" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="C491" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="D491" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E491" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F486" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G486" s="8" t="s">
+      <c r="F491" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="G491" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="487" ht="51" spans="1:7">
-      <c r="A487" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B487" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="C487" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D487" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E487" s="7" t="s">
+    <row r="492" ht="25.5" spans="1:7">
+      <c r="A492" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="C492" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="D492" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E492" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F487" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G487" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="488" ht="51" spans="1:7">
-      <c r="A488" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B488" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="C488" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="D488" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E488" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F488" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G488" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="489" ht="51" spans="1:7">
-      <c r="A489" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B489" s="7" t="s">
-        <v>782</v>
-      </c>
-      <c r="C489" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="D489" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E489" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F489" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G489" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="490" ht="51" spans="1:7">
-      <c r="A490" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B490" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C490" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D490" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E490" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F490" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G490" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="491" ht="51" spans="1:7">
-      <c r="A491" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B491" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="C491" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="D491" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E491" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F491" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G491" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="492" ht="51" spans="1:7">
-      <c r="A492" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B492" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="C492" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="D492" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E492" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F492" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G492" s="8" t="s">
+      <c r="F492" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="G492" s="5" t="s">
         <v>745</v>
       </c>
     </row>
@@ -15043,19 +15232,19 @@
       <c r="F493" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="G493" s="4" t="s">
+      <c r="G493" s="3" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="494" ht="25.5" spans="1:7">
+    <row r="494" spans="1:7">
       <c r="A494" s="3" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>31</v>
@@ -15064,366 +15253,366 @@
         <v>51</v>
       </c>
       <c r="F494" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="G494" s="3" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7">
+      <c r="A495" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E495" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F495" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7">
+      <c r="A496" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C496" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E496" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F496" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="G496" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7">
+      <c r="A497" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E497" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F497" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="G497" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7">
+      <c r="A498" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B498" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E498" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F498" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="G498" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7">
+      <c r="A499" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E499" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F499" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="G499" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7">
+      <c r="A500" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E500" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F500" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G500" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7">
+      <c r="A501" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E501" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F501" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="G501" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="502" ht="25.5" spans="1:7">
+      <c r="A502" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D502" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E502" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F502" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="G502" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="503" ht="25.5" spans="1:7">
+      <c r="A503" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="D503" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E503" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F503" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="G503" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="504" ht="25.5" spans="1:7">
+      <c r="A504" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D504" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E504" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F504" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="G504" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="505" ht="25.5" spans="1:7">
+      <c r="A505" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B505" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D505" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E505" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F505" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="G505" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="506" ht="25.5" spans="1:7">
+      <c r="A506" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D506" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E506" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F506" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="G506" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="507" ht="25.5" spans="1:7">
+      <c r="A507" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D507" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E507" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F507" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="G507" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="508" ht="25.5" spans="1:7">
+      <c r="A508" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="G494" s="4" t="s">
+      <c r="B508" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D508" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E508" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F508" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="G508" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="495" ht="25.5" spans="1:7">
-      <c r="A495" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="B495" s="5" t="s">
-        <v>796</v>
-      </c>
-      <c r="C495" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="D495" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E495" s="5" t="s">
+    <row r="509" ht="25.5" spans="1:7">
+      <c r="A509" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="D509" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E509" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F495" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G495" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="496" ht="25.5" spans="1:7">
-      <c r="A496" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="B496" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="C496" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="D496" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E496" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F496" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G496" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="497" spans="1:7">
-      <c r="A497" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B497" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="C497" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="D497" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E497" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F497" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G497" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="498" spans="1:7">
-      <c r="A498" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B498" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="C498" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="D498" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E498" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F498" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G498" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="499" spans="1:7">
-      <c r="A499" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B499" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="C499" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="D499" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E499" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F499" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G499" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="500" spans="1:7">
-      <c r="A500" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B500" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="C500" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="D500" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E500" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F500" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G500" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="501" spans="1:7">
-      <c r="A501" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B501" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="C501" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="D501" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E501" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F501" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G501" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="502" ht="38.25" spans="1:7">
-      <c r="A502" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B502" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="C502" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D502" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E502" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F502" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G502" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="503" ht="38.25" spans="1:7">
-      <c r="A503" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B503" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="C503" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D503" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E503" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F503" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G503" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="504" ht="51" spans="1:7">
-      <c r="A504" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B504" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="C504" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="D504" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E504" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F504" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G504" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="505" ht="51" spans="1:7">
-      <c r="A505" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B505" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="C505" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D505" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E505" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F505" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G505" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="506" ht="51" spans="1:7">
-      <c r="A506" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B506" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="C506" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D506" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E506" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F506" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G506" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="507" ht="51" spans="1:7">
-      <c r="A507" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B507" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="C507" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="D507" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E507" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F507" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G507" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="508" ht="51" spans="1:7">
-      <c r="A508" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B508" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="C508" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="D508" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E508" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F508" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G508" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="509" ht="51" spans="1:7">
-      <c r="A509" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B509" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="C509" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="D509" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E509" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F509" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G509" s="8" t="s">
+      <c r="F509" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="G509" s="5" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="510" spans="1:7">
       <c r="A510" s="3" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
       <c r="D510" s="3" t="s">
         <v>29</v>
@@ -15432,24 +15621,24 @@
         <v>63</v>
       </c>
       <c r="F510" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="G510" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G510" s="3" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="511" spans="1:7">
       <c r="A511" s="3" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="C511" s="3" t="s">
         <v>751</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>821</v>
+        <v>846</v>
       </c>
       <c r="E511" s="3" t="s">
         <v>63</v>
@@ -15457,16 +15646,16 @@
       <c r="F511" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="G511" s="4" t="s">
+      <c r="G511" s="3" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="512" spans="1:7">
       <c r="A512" s="3" t="s">
-        <v>822</v>
+        <v>847</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>823</v>
+        <v>848</v>
       </c>
       <c r="C512" s="3" t="s">
         <v>751</v>
@@ -15480,387 +15669,387 @@
       <c r="F512" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="G512" s="4" t="s">
+      <c r="G512" s="3" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="513" ht="25.5" spans="1:7">
-      <c r="A513" s="5" t="s">
+    <row r="513" spans="1:7">
+      <c r="A513" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B513" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="C513" s="5" t="s">
+      <c r="B513" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C513" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D513" s="5" t="s">
+      <c r="D513" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E513" s="5" t="s">
+      <c r="E513" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F513" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G513" s="6" t="s">
+      <c r="F513" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="G513" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="514" ht="25.5" spans="1:7">
-      <c r="A514" s="5" t="s">
+    <row r="514" spans="1:7">
+      <c r="A514" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B514" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="C514" s="5" t="s">
+      <c r="B514" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C514" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D514" s="5" t="s">
+      <c r="D514" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E514" s="5" t="s">
+      <c r="E514" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F514" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G514" s="6" t="s">
+      <c r="F514" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="G514" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="515" spans="1:7">
-      <c r="A515" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B515" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="C515" s="5" t="s">
+      <c r="A515" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C515" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D515" s="5" t="s">
+      <c r="D515" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E515" s="5" t="s">
+      <c r="E515" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F515" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G515" s="6" t="s">
+      <c r="F515" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="G515" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="516" spans="1:7">
-      <c r="A516" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B516" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="C516" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D516" s="5" t="s">
+      <c r="A516" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="D516" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E516" s="5" t="s">
+      <c r="E516" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F516" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G516" s="6" t="s">
+      <c r="F516" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="G516" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="517" spans="1:7">
-      <c r="A517" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B517" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="C517" s="5" t="s">
+      <c r="A517" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="D517" s="5" t="s">
+      <c r="B517" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D517" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E517" s="5" t="s">
+      <c r="E517" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F517" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G517" s="6" t="s">
+      <c r="F517" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="G517" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="518" spans="1:7">
-      <c r="A518" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B518" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="C518" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="D518" s="5" t="s">
+      <c r="A518" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D518" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E518" s="5" t="s">
+      <c r="E518" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F518" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G518" s="6" t="s">
+      <c r="F518" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="G518" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="519" ht="51" spans="1:7">
-      <c r="A519" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B519" s="7" t="s">
-        <v>830</v>
-      </c>
-      <c r="C519" s="7" t="s">
+    <row r="519" ht="25.5" spans="1:7">
+      <c r="A519" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C519" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D519" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E519" s="7" t="s">
+      <c r="D519" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E519" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F519" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G519" s="8" t="s">
+      <c r="F519" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="G519" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="520" ht="51" spans="1:7">
-      <c r="A520" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B520" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="C520" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="D520" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E520" s="7" t="s">
+    <row r="520" ht="25.5" spans="1:7">
+      <c r="A520" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D520" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E520" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F520" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G520" s="8" t="s">
+      <c r="F520" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="G520" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="521" ht="51" spans="1:7">
-      <c r="A521" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B521" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="C521" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="D521" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E521" s="7" t="s">
+    <row r="521" ht="25.5" spans="1:7">
+      <c r="A521" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D521" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E521" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F521" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G521" s="8" t="s">
+      <c r="F521" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="G521" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="522" ht="51" spans="1:7">
-      <c r="A522" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B522" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="C522" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="D522" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E522" s="7" t="s">
+    <row r="522" ht="25.5" spans="1:7">
+      <c r="A522" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="D522" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E522" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F522" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G522" s="8" t="s">
+      <c r="F522" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="G522" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="523" ht="38.25" spans="1:7">
-      <c r="A523" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B523" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="C523" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D523" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E523" s="7" t="s">
+    <row r="523" ht="25.5" spans="1:7">
+      <c r="A523" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D523" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E523" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F523" s="7" t="s">
+      <c r="F523" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="G523" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="524" ht="25.5" spans="1:7">
+      <c r="A524" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="G523" s="8" t="s">
+      <c r="B524" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="D524" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E524" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F524" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="G524" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="524" ht="38.25" spans="1:7">
-      <c r="A524" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B524" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="C524" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D524" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E524" s="7" t="s">
+    <row r="525" ht="25.5" spans="1:7">
+      <c r="A525" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D525" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E525" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F524" s="7" t="s">
+      <c r="F525" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="G525" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="526" ht="25.5" spans="1:7">
+      <c r="A526" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="G524" s="8" t="s">
+      <c r="B526" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="D526" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E526" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F526" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="G526" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="525" ht="38.25" spans="1:7">
-      <c r="A525" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B525" s="7" t="s">
-        <v>838</v>
-      </c>
-      <c r="C525" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D525" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E525" s="7" t="s">
+    <row r="527" ht="25.5" spans="1:7">
+      <c r="A527" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E527" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F525" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G525" s="8" t="s">
+      <c r="F527" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="G527" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="526" ht="38.25" spans="1:7">
-      <c r="A526" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B526" s="7" t="s">
-        <v>839</v>
-      </c>
-      <c r="C526" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="D526" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E526" s="7" t="s">
+    <row r="528" ht="25.5" spans="1:7">
+      <c r="A528" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D528" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="E528" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F526" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G526" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="527" ht="51" spans="1:7">
-      <c r="A527" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B527" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="C527" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D527" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E527" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F527" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G527" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="528" ht="51" spans="1:7">
-      <c r="A528" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B528" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="C528" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="D528" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E528" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F528" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G528" s="8" t="s">
+      <c r="F528" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="G528" s="5" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" s="3" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>29</v>
@@ -15869,18 +16058,18 @@
         <v>76</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="G529" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G529" s="3" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="530" ht="25.5" spans="1:7">
       <c r="A530" s="3" t="s">
-        <v>842</v>
+        <v>882</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>843</v>
+        <v>883</v>
       </c>
       <c r="C530" s="3" t="s">
         <v>371</v>
@@ -15892,377 +16081,377 @@
         <v>76</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="G530" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="G530" s="3" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="531" ht="25.5" spans="1:7">
-      <c r="A531" s="5" t="s">
+    <row r="531" spans="1:7">
+      <c r="A531" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B531" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="C531" s="5" t="s">
+      <c r="B531" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="C531" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D531" s="5" t="s">
+      <c r="D531" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E531" s="5" t="s">
+      <c r="E531" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F531" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G531" s="6" t="s">
+      <c r="F531" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="G531" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="532" spans="1:7">
-      <c r="A532" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B532" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="C532" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="D532" s="5" t="s">
+      <c r="A532" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D532" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E532" s="5" t="s">
+      <c r="E532" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F532" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G532" s="6" t="s">
+      <c r="F532" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="G532" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="533" spans="1:7">
-      <c r="A533" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B533" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="C533" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="D533" s="5" t="s">
+      <c r="A533" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D533" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E533" s="5" t="s">
+      <c r="E533" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F533" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G533" s="6" t="s">
+      <c r="F533" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="G533" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="534" spans="1:7">
-      <c r="A534" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B534" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="C534" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="D534" s="5" t="s">
+      <c r="A534" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="D534" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E534" s="5" t="s">
+      <c r="E534" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F534" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G534" s="6" t="s">
+      <c r="F534" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G534" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="535" spans="1:7">
-      <c r="A535" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B535" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="C535" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="D535" s="5" t="s">
+      <c r="A535" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D535" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E535" s="5" t="s">
+      <c r="E535" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F535" s="5" t="s">
+      <c r="F535" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="G535" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7">
+      <c r="A536" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="G535" s="6" t="s">
+      <c r="B536" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E536" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F536" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="G536" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
-      <c r="A536" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B536" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="C536" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="D536" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E536" s="5" t="s">
+    <row r="537" ht="25.5" spans="1:7">
+      <c r="A537" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E537" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F536" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G536" s="6" t="s">
+      <c r="F537" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="G537" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="537" ht="38.25" spans="1:7">
-      <c r="A537" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B537" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="C537" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D537" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E537" s="7" t="s">
+    <row r="538" ht="25.5" spans="1:7">
+      <c r="A538" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E538" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F537" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G537" s="8" t="s">
+      <c r="F538" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="G538" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="538" ht="38.25" spans="1:7">
-      <c r="A538" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B538" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="C538" s="7" t="s">
+    <row r="539" ht="25.5" spans="1:7">
+      <c r="A539" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D539" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D538" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E538" s="7" t="s">
+      <c r="E539" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F538" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G538" s="8" t="s">
+      <c r="F539" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="G539" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="539" ht="51" spans="1:7">
-      <c r="A539" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B539" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="C539" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D539" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E539" s="7" t="s">
+    <row r="540" ht="25.5" spans="1:7">
+      <c r="A540" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D540" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E540" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F539" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G539" s="8" t="s">
+      <c r="F540" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="G540" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="540" ht="51" spans="1:7">
-      <c r="A540" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B540" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="C540" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="D540" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E540" s="7" t="s">
+    <row r="541" ht="25.5" spans="1:7">
+      <c r="A541" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E541" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F540" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G540" s="8" t="s">
+      <c r="F541" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="G541" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="541" ht="51" spans="1:7">
-      <c r="A541" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B541" s="7" t="s">
-        <v>855</v>
-      </c>
-      <c r="C541" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="D541" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E541" s="7" t="s">
+    <row r="542" ht="25.5" spans="1:7">
+      <c r="A542" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D542" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E542" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F541" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G541" s="8" t="s">
+      <c r="F542" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="G542" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="542" ht="51" spans="1:7">
-      <c r="A542" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B542" s="7" t="s">
-        <v>856</v>
-      </c>
-      <c r="C542" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D542" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E542" s="7" t="s">
+    <row r="543" ht="25.5" spans="1:7">
+      <c r="A543" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="D543" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E543" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F542" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G542" s="8" t="s">
+      <c r="F543" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="G543" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="543" ht="51" spans="1:7">
-      <c r="A543" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B543" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="C543" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="D543" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E543" s="7" t="s">
+    <row r="544" ht="25.5" spans="1:7">
+      <c r="A544" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="D544" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E544" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F543" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G543" s="8" t="s">
+      <c r="F544" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="G544" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="544" ht="51" spans="1:7">
-      <c r="A544" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B544" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="C544" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="D544" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E544" s="7" t="s">
+    <row r="545" ht="25.5" spans="1:7">
+      <c r="A545" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D545" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E545" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F544" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G544" s="8" t="s">
+      <c r="F545" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="G545" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="545" ht="51" spans="1:7">
-      <c r="A545" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B545" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="C545" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D545" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E545" s="7" t="s">
+    <row r="546" ht="25.5" spans="1:7">
+      <c r="A546" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D546" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E546" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F545" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G545" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="546" ht="51" spans="1:7">
-      <c r="A546" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B546" s="7" t="s">
-        <v>860</v>
-      </c>
-      <c r="C546" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="D546" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E546" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F546" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G546" s="8" t="s">
+      <c r="F546" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="G546" s="5" t="s">
         <v>745</v>
       </c>
     </row>
@@ -16285,19 +16474,19 @@
       <c r="F547" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="G547" s="4" t="s">
+      <c r="G547" s="3" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="548" ht="25.5" spans="1:7">
       <c r="A548" s="3" t="s">
-        <v>861</v>
+        <v>914</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>862</v>
+        <v>915</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>863</v>
+        <v>916</v>
       </c>
       <c r="D548" s="3" t="s">
         <v>31</v>
@@ -16306,377 +16495,377 @@
         <v>35</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="G548" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="G548" s="3" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="549" ht="25.5" spans="1:7">
-      <c r="A549" s="5" t="s">
+    <row r="549" spans="1:7">
+      <c r="A549" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="B549" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="C549" s="5" t="s">
+      <c r="B549" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C549" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D549" s="5" t="s">
+      <c r="D549" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E549" s="5" t="s">
+      <c r="E549" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F549" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G549" s="6" t="s">
+      <c r="F549" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="G549" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="550" spans="1:7">
-      <c r="A550" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="B550" s="5" t="s">
-        <v>866</v>
-      </c>
-      <c r="C550" s="5" t="s">
+      <c r="A550" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C550" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D550" s="5" t="s">
+      <c r="D550" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E550" s="5" t="s">
+      <c r="E550" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F550" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="G550" s="6" t="s">
+      <c r="F550" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="G550" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="551" spans="1:7">
-      <c r="A551" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B551" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="C551" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="D551" s="5" t="s">
+      <c r="A551" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="D551" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E551" s="5" t="s">
+      <c r="E551" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F551" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G551" s="6" t="s">
+      <c r="F551" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="G551" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="552" spans="1:7">
-      <c r="A552" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B552" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="C552" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D552" s="5" t="s">
+      <c r="A552" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="D552" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E552" s="5" t="s">
+      <c r="E552" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F552" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="G552" s="6" t="s">
+      <c r="F552" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="G552" s="4" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="553" spans="1:7">
-      <c r="A553" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B553" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="C553" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="D553" s="5" t="s">
+      <c r="A553" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D553" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E553" s="5" t="s">
+      <c r="E553" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F553" s="5" t="s">
+      <c r="F553" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G553" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7">
+      <c r="A554" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="G553" s="6" t="s">
+      <c r="B554" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C554" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E554" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F554" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="G554" s="4" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="554" spans="1:7">
-      <c r="A554" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="B554" s="5" t="s">
-        <v>870</v>
-      </c>
-      <c r="C554" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="D554" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E554" s="5" t="s">
+    <row r="555" ht="25.5" spans="1:7">
+      <c r="A555" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D555" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E555" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F554" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="G554" s="6" t="s">
+      <c r="F555" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="G555" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="555" ht="38.25" spans="1:7">
-      <c r="A555" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B555" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="C555" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D555" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E555" s="7" t="s">
+    <row r="556" ht="25.5" spans="1:7">
+      <c r="A556" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="D556" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E556" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F555" s="7" t="s">
+      <c r="F556" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="G556" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="557" ht="25.5" spans="1:7">
+      <c r="A557" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="G555" s="8" t="s">
+      <c r="B557" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D557" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E557" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F557" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="G557" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="556" ht="38.25" spans="1:7">
-      <c r="A556" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B556" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="C556" s="7" t="s">
+    <row r="558" ht="25.5" spans="1:7">
+      <c r="A558" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="D558" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="D556" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E556" s="7" t="s">
+      <c r="E558" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F556" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G556" s="8" t="s">
+      <c r="F558" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="G558" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="557" ht="38.25" spans="1:7">
-      <c r="A557" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B557" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="C557" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D557" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E557" s="7" t="s">
+    <row r="559" ht="25.5" spans="1:7">
+      <c r="A559" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D559" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E559" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F557" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G557" s="8" t="s">
+      <c r="F559" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="G559" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="558" ht="38.25" spans="1:7">
-      <c r="A558" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="B558" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="C558" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D558" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E558" s="7" t="s">
+    <row r="560" ht="25.5" spans="1:7">
+      <c r="A560" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D560" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E560" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F558" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="G558" s="8" t="s">
+      <c r="F560" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="G560" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="559" ht="51" spans="1:7">
-      <c r="A559" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B559" s="7" t="s">
-        <v>875</v>
-      </c>
-      <c r="C559" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="D559" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E559" s="7" t="s">
+    <row r="561" ht="25.5" spans="1:7">
+      <c r="A561" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D561" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E561" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F559" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G559" s="8" t="s">
+      <c r="F561" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="G561" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="560" ht="51" spans="1:7">
-      <c r="A560" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="B560" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="C560" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D560" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E560" s="7" t="s">
+    <row r="562" ht="25.5" spans="1:7">
+      <c r="A562" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="D562" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E562" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F560" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="G560" s="8" t="s">
+      <c r="F562" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="G562" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="561" ht="51" spans="1:7">
-      <c r="A561" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B561" s="7" t="s">
-        <v>877</v>
-      </c>
-      <c r="C561" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="D561" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E561" s="7" t="s">
+    <row r="563" ht="25.5" spans="1:7">
+      <c r="A563" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E563" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F561" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G561" s="8" t="s">
+      <c r="F563" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="G563" s="5" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="562" ht="51" spans="1:7">
-      <c r="A562" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B562" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="C562" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="D562" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E562" s="7" t="s">
+    <row r="564" ht="25.5" spans="1:7">
+      <c r="A564" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="D564" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E564" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F562" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G562" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="563" ht="51" spans="1:7">
-      <c r="A563" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B563" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="C563" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="D563" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E563" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F563" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G563" s="8" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="564" ht="51" spans="1:7">
-      <c r="A564" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="B564" s="7" t="s">
-        <v>880</v>
-      </c>
-      <c r="C564" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="D564" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="E564" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F564" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="G564" s="8" t="s">
+      <c r="F564" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="G564" s="5" t="s">
         <v>745</v>
       </c>
     </row>

--- a/dataEDT-ELT-S2-2026.xlsx
+++ b/dataEDT-ELT-S2-2026.xlsx
@@ -2258,7 +2258,7 @@
     <t>Cours-Mathématiques 1</t>
   </si>
   <si>
-    <t>Cours-MAT1-MCIL1</t>
+    <t>Cours-MAT1-L1MCIL</t>
   </si>
   <si>
     <t>Bahlil</t>
@@ -2267,13 +2267,13 @@
     <t>A10/Section B</t>
   </si>
   <si>
-    <t>MCIL1</t>
+    <t>L1MCIL</t>
   </si>
   <si>
     <t>Cours-Structure de la matière</t>
   </si>
   <si>
-    <t>Cours-SM-MCIL1</t>
+    <t>Cours-SM-L1MCIL</t>
   </si>
   <si>
     <t>Badis</t>
@@ -2282,7 +2282,7 @@
     <t>TD-Informatique 1</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G2</t>
+    <t>TD-INFO1-L1MCIL-G2</t>
   </si>
   <si>
     <t>Non identifié</t>
@@ -2291,7 +2291,7 @@
     <t>Salle micro/G2</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G7</t>
+    <t>TD-INFO1-L1MCIL-G7</t>
   </si>
   <si>
     <t>Salle micro/G7</t>
@@ -2300,13 +2300,13 @@
     <t>TD-Mathématiques 1</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G1</t>
+    <t>TD-MAT1-L1MCIL-G1</t>
   </si>
   <si>
     <t>A08/G1</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G6</t>
+    <t>TD-MAT1-L1MCIL-G6</t>
   </si>
   <si>
     <t>A08/G6</t>
@@ -2315,7 +2315,7 @@
     <t>TD-Physique 1</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G3</t>
+    <t>TD-PHY1-L1MCIL-G3</t>
   </si>
   <si>
     <t>SACI</t>
@@ -2324,7 +2324,7 @@
     <t>A09/G3</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G8</t>
+    <t>TD-PHY1-L1MCIL-G8</t>
   </si>
   <si>
     <t>Zidi</t>
@@ -2336,7 +2336,7 @@
     <t>TD-Structure de la matière</t>
   </si>
   <si>
-    <t>TD-SM-MCIL1-G5</t>
+    <t>TD-SM-L1MCIL-G5</t>
   </si>
   <si>
     <t>HEMMAR</t>
@@ -2348,7 +2348,7 @@
     <t>TP-Informatique 1</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG05</t>
+    <t>TP-INFO1-L1MCIL-SG05</t>
   </si>
   <si>
     <t>13h-14h30</t>
@@ -2357,7 +2357,7 @@
     <t>Salle micro2/SG05</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG06</t>
+    <t>TP-INFO1-L1MCIL-SG06</t>
   </si>
   <si>
     <t>BENCELLA</t>
@@ -2366,7 +2366,7 @@
     <t>Salle micro2/SG06</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG15</t>
+    <t>TP-INFO1-L1MCIL-SG15</t>
   </si>
   <si>
     <t>BENHALOUCHE</t>
@@ -2375,7 +2375,7 @@
     <t>Salle micro2/SG15</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG16</t>
+    <t>TP-INFO1-L1MCIL-SG16</t>
   </si>
   <si>
     <t>ZIAN</t>
@@ -2387,19 +2387,19 @@
     <t>TP-Chimie 1</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG01</t>
+    <t>TP-TPCH1-L1MCIL-SG01</t>
   </si>
   <si>
     <t>Labo Chimie/SG01</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG02</t>
+    <t>TP-TPCH1-L1MCIL-SG02</t>
   </si>
   <si>
     <t>Labo Chimie/SG02</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG11</t>
+    <t>TP-TPCH1-L1MCIL-SG11</t>
   </si>
   <si>
     <t>MOKADEM</t>
@@ -2408,7 +2408,7 @@
     <t>Labo Chimie/SG11</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG12</t>
+    <t>TP-TPCH1-L1MCIL-SG12</t>
   </si>
   <si>
     <t>ND</t>
@@ -2420,7 +2420,7 @@
     <t>TP-Physique 1</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG07</t>
+    <t>TP-TPPHY1-L1MCIL-SG07</t>
   </si>
   <si>
     <t>BENSSADIK</t>
@@ -2429,7 +2429,7 @@
     <t>Labo Physique 1/SG07</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG08</t>
+    <t>TP-TPPHY1-L1MCIL-SG08</t>
   </si>
   <si>
     <t>BOULARAF</t>
@@ -2441,7 +2441,7 @@
     <t>Cours-Informatique 1</t>
   </si>
   <si>
-    <t>Cours-INFO1-MCIL1</t>
+    <t>Cours-INFO1-L1MCIL</t>
   </si>
   <si>
     <t>Beddad</t>
@@ -2450,19 +2450,19 @@
     <t>A10/Section A</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G3</t>
+    <t>TD-INFO1-L1MCIL-G3</t>
   </si>
   <si>
     <t>Salle micro/G3</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G8</t>
+    <t>TD-INFO1-L1MCIL-G8</t>
   </si>
   <si>
     <t>Salle micro/G8</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G2</t>
+    <t>TD-MAT1-L1MCIL-G2</t>
   </si>
   <si>
     <t>ABDELI</t>
@@ -2471,25 +2471,25 @@
     <t>A08/G2</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G7</t>
+    <t>TD-MAT1-L1MCIL-G7</t>
   </si>
   <si>
     <t>A08/G7</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G4</t>
+    <t>TD-PHY1-L1MCIL-G4</t>
   </si>
   <si>
     <t>A09/G4</t>
   </si>
   <si>
-    <t>TD-SM-MCIL1-G1</t>
+    <t>TD-SM-L1MCIL-G1</t>
   </si>
   <si>
     <t>A09/G1</t>
   </si>
   <si>
-    <t>TD-SM-MCIL1-G6</t>
+    <t>TD-SM-L1MCIL-G6</t>
   </si>
   <si>
     <t>MECHTEM</t>
@@ -2498,43 +2498,43 @@
     <t>A09/G6</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG07</t>
+    <t>TP-INFO1-L1MCIL-SG07</t>
   </si>
   <si>
     <t>Salle micro2/SG07</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG08</t>
+    <t>TP-INFO1-L1MCIL-SG08</t>
   </si>
   <si>
     <t>Salle micro2/SG08</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG03</t>
+    <t>TP-TPCH1-L1MCIL-SG03</t>
   </si>
   <si>
     <t>Labo Chimie/SG03</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG04</t>
+    <t>TP-TPCH1-L1MCIL-SG04</t>
   </si>
   <si>
     <t>Labo Chimie/SG04</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG13</t>
+    <t>TP-TPCH1-L1MCIL-SG13</t>
   </si>
   <si>
     <t>Labo Chimie/SG13</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG14</t>
+    <t>TP-TPCH1-L1MCIL-SG14</t>
   </si>
   <si>
     <t>Labo Chimie/SG14</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG09</t>
+    <t>TP-TPPHY1-L1MCIL-SG09</t>
   </si>
   <si>
     <t>DRIEF</t>
@@ -2543,7 +2543,7 @@
     <t>Labo Physique /SG09</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG10</t>
+    <t>TP-TPPHY1-L1MCIL-SG10</t>
   </si>
   <si>
     <t>Mekhalef</t>
@@ -2555,7 +2555,7 @@
     <t>Cours-Physique 1</t>
   </si>
   <si>
-    <t>Cours-PHY1-MCIL1</t>
+    <t>Cours-PHY1-L1MCIL</t>
   </si>
   <si>
     <t>Bendaoud</t>
@@ -2567,7 +2567,7 @@
     <t>Cours-Méthodologie de la rédaction</t>
   </si>
   <si>
-    <t>Cours-MR-MCIL1</t>
+    <t>Cours-MR-L1MCIL</t>
   </si>
   <si>
     <t>9h30-10h30</t>
@@ -2576,49 +2576,49 @@
     <t>Cours-Langue étrangère 1</t>
   </si>
   <si>
-    <t>Cours-LE1-MCIL1</t>
-  </si>
-  <si>
-    <t>TD-INFO1-MCIL1-G1</t>
+    <t>Cours-LE1-L1MCIL</t>
+  </si>
+  <si>
+    <t>TD-INFO1-L1MCIL-G1</t>
   </si>
   <si>
     <t>Salle micro/G1</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G6</t>
+    <t>TD-INFO1-L1MCIL-G6</t>
   </si>
   <si>
     <t>Salle micro/G6</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G5</t>
+    <t>TD-MAT1-L1MCIL-G5</t>
   </si>
   <si>
     <t>A08/G5</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G2</t>
+    <t>TD-PHY1-L1MCIL-G2</t>
   </si>
   <si>
     <t>A09/G2</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G7</t>
+    <t>TD-PHY1-L1MCIL-G7</t>
   </si>
   <si>
     <t>A09/G7</t>
   </si>
   <si>
-    <t>TD-SM-MCIL1-G4</t>
-  </si>
-  <si>
-    <t>TP-TPPHY1-MCIL1-SG05</t>
+    <t>TD-SM-L1MCIL-G4</t>
+  </si>
+  <si>
+    <t>TP-TPPHY1-L1MCIL-SG05</t>
   </si>
   <si>
     <t>Labo Physique /SG05</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG06</t>
+    <t>TP-TPPHY1-L1MCIL-SG06</t>
   </si>
   <si>
     <t>TURKI</t>
@@ -2627,19 +2627,19 @@
     <t>Labo Physique /SG06</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG15</t>
+    <t>TP-TPPHY1-L1MCIL-SG15</t>
   </si>
   <si>
     <t>Labo Physique /SG15</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG16</t>
+    <t>TP-TPPHY1-L1MCIL-SG16</t>
   </si>
   <si>
     <t>Labo Physique /SG16</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG03</t>
+    <t>TP-INFO1-L1MCIL-SG03</t>
   </si>
   <si>
     <t>14h30-16h</t>
@@ -2648,31 +2648,31 @@
     <t>Salle micro2/SG03</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG04</t>
+    <t>TP-INFO1-L1MCIL-SG04</t>
   </si>
   <si>
     <t>Salle micro2/SG04</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG13</t>
+    <t>TP-INFO1-L1MCIL-SG13</t>
   </si>
   <si>
     <t>Salle micro2/SG13</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG14</t>
+    <t>TP-INFO1-L1MCIL-SG14</t>
   </si>
   <si>
     <t>Salle micro2/SG14</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG09</t>
+    <t>TP-TPCH1-L1MCIL-SG09</t>
   </si>
   <si>
     <t>Labo Chimie/SG09</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG10</t>
+    <t>TP-TPCH1-L1MCIL-SG10</t>
   </si>
   <si>
     <t>Labo Chimie/SG10</t>
@@ -2681,94 +2681,94 @@
     <t>Cours-Les métiers en Sciences et Technologies 1</t>
   </si>
   <si>
-    <t>Cours-LMST-MCIL1</t>
+    <t>Cours-LMST-L1MCIL</t>
   </si>
   <si>
     <t>A11/Section B</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G4</t>
+    <t>TD-INFO1-L1MCIL-G4</t>
   </si>
   <si>
     <t>Salle micro/G4</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G3</t>
+    <t>TD-MAT1-L1MCIL-G3</t>
   </si>
   <si>
     <t>A08/G3</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G8</t>
+    <t>TD-MAT1-L1MCIL-G8</t>
   </si>
   <si>
     <t>A08/G8</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G5</t>
-  </si>
-  <si>
-    <t>TD-SM-MCIL1-G2</t>
-  </si>
-  <si>
-    <t>TD-SM-MCIL1-G7</t>
-  </si>
-  <si>
-    <t>TP-INFO1-MCIL1-SG09</t>
+    <t>TD-PHY1-L1MCIL-G5</t>
+  </si>
+  <si>
+    <t>TD-SM-L1MCIL-G2</t>
+  </si>
+  <si>
+    <t>TD-SM-L1MCIL-G7</t>
+  </si>
+  <si>
+    <t>TP-INFO1-L1MCIL-SG09</t>
   </si>
   <si>
     <t>Salle micro2/SG09</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG10</t>
+    <t>TP-INFO1-L1MCIL-SG10</t>
   </si>
   <si>
     <t>Salle micro2/SG10</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG05</t>
+    <t>TP-TPCH1-L1MCIL-SG05</t>
   </si>
   <si>
     <t>Labo Chimie/SG05</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG06</t>
+    <t>TP-TPCH1-L1MCIL-SG06</t>
   </si>
   <si>
     <t>Labo Chimie/SG06</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG15</t>
+    <t>TP-TPCH1-L1MCIL-SG15</t>
   </si>
   <si>
     <t>Labo Chimie/SG15</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG16</t>
+    <t>TP-TPCH1-L1MCIL-SG16</t>
   </si>
   <si>
     <t>Labo Chimie/SG16</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG01</t>
+    <t>TP-TPPHY1-L1MCIL-SG01</t>
   </si>
   <si>
     <t>Labo Physique 1/SG01</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG02</t>
+    <t>TP-TPPHY1-L1MCIL-SG02</t>
   </si>
   <si>
     <t>Labo Physique 2/SG02</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG11</t>
+    <t>TP-TPPHY1-L1MCIL-SG11</t>
   </si>
   <si>
     <t>Labo Physique 3/SG11</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG12</t>
+    <t>TP-TPPHY1-L1MCIL-SG12</t>
   </si>
   <si>
     <t>Labo Physique 4/SG12</t>
@@ -2777,7 +2777,7 @@
     <t>Cours-Dimension éthique et déontologie</t>
   </si>
   <si>
-    <t>Cours-DE-MCIL1</t>
+    <t>Cours-DE-L1MCIL</t>
   </si>
   <si>
     <t>Ouari</t>
@@ -2786,88 +2786,88 @@
     <t>A10/Section A-B</t>
   </si>
   <si>
-    <t>TD-INFO1-MCIL1-G5</t>
+    <t>TD-INFO1-L1MCIL-G5</t>
   </si>
   <si>
     <t>Salle micro</t>
   </si>
   <si>
-    <t>TD-MAT1-MCIL1-G4</t>
+    <t>TD-MAT1-L1MCIL-G4</t>
   </si>
   <si>
     <t>A08/G1-G8</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G1</t>
+    <t>TD-PHY1-L1MCIL-G1</t>
   </si>
   <si>
     <t>A09/G1-G8</t>
   </si>
   <si>
-    <t>TD-PHY1-MCIL1-G6</t>
-  </si>
-  <si>
-    <t>TD-SM-MCIL1-G3</t>
-  </si>
-  <si>
-    <t>TD-SM-MCIL1-G8</t>
-  </si>
-  <si>
-    <t>TP-INFO1-MCIL1-SG01</t>
+    <t>TD-PHY1-L1MCIL-G6</t>
+  </si>
+  <si>
+    <t>TD-SM-L1MCIL-G3</t>
+  </si>
+  <si>
+    <t>TD-SM-L1MCIL-G8</t>
+  </si>
+  <si>
+    <t>TP-INFO1-L1MCIL-SG01</t>
   </si>
   <si>
     <t>Salle micro2/SG01</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG02</t>
+    <t>TP-INFO1-L1MCIL-SG02</t>
   </si>
   <si>
     <t>Salle micro2/SG02</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG11</t>
+    <t>TP-INFO1-L1MCIL-SG11</t>
   </si>
   <si>
     <t>Salle micro2/SG11</t>
   </si>
   <si>
-    <t>TP-INFO1-MCIL1-SG12</t>
+    <t>TP-INFO1-L1MCIL-SG12</t>
   </si>
   <si>
     <t>Salle micro2/SG12</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG07</t>
+    <t>TP-TPCH1-L1MCIL-SG07</t>
   </si>
   <si>
     <t>Labo Chimie/SG07</t>
   </si>
   <si>
-    <t>TP-TPCH1-MCIL1-SG08</t>
+    <t>TP-TPCH1-L1MCIL-SG08</t>
   </si>
   <si>
     <t>Labo Chimie/SG08</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG03</t>
+    <t>TP-TPPHY1-L1MCIL-SG03</t>
   </si>
   <si>
     <t>Labo Physique 1/SG03</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG04</t>
+    <t>TP-TPPHY1-L1MCIL-SG04</t>
   </si>
   <si>
     <t>Labo Physique 1/SG04</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG13</t>
+    <t>TP-TPPHY1-L1MCIL-SG13</t>
   </si>
   <si>
     <t>Labo Physique 1/SG13</t>
   </si>
   <si>
-    <t>TP-TPPHY1-MCIL1-SG14</t>
+    <t>TP-TPPHY1-L1MCIL-SG14</t>
   </si>
   <si>
     <t>Labo Physique 1/SG14</t>
@@ -14822,7 +14822,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" ht="25.5" spans="1:7">
       <c r="A476" s="4" t="s">
         <v>749</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" ht="25.5" spans="1:7">
       <c r="A477" s="4" t="s">
         <v>749</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" ht="25.5" spans="1:7">
       <c r="A494" s="3" t="s">
         <v>802</v>
       </c>
@@ -15259,7 +15259,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" ht="25.5" spans="1:7">
       <c r="A495" s="4" t="s">
         <v>749</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" ht="25.5" spans="1:7">
       <c r="A496" s="4" t="s">
         <v>749</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" ht="25.5" spans="1:7">
       <c r="A513" s="4" t="s">
         <v>749</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" ht="25.5" spans="1:7">
       <c r="A514" s="4" t="s">
         <v>749</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" ht="25.5" spans="1:7">
       <c r="A531" s="4" t="s">
         <v>749</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" ht="25.5" spans="1:7">
       <c r="A549" s="4" t="s">
         <v>749</v>
       </c>
